--- a/Sensitivity_Output/Sensitivity_Penalty.xlsx
+++ b/Sensitivity_Output/Sensitivity_Penalty.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,27 +429,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>penalty</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>util_std_dev</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>avg_distance_km</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>overcap_weeks_total</t>
         </is>
@@ -453,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>9.15</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>24.76</v>
+        <v>24.79</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="3">
@@ -472,10 +484,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>9.15</v>
+        <v>0.34</v>
       </c>
       <c r="D3" t="n">
-        <v>24.76</v>
+        <v>24.8</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -491,10 +503,10 @@
         <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>9.15</v>
+        <v>0.34</v>
       </c>
       <c r="D4" t="n">
-        <v>24.76</v>
+        <v>24.8</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -510,10 +522,10 @@
         <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>9.15</v>
+        <v>0.34</v>
       </c>
       <c r="D5" t="n">
-        <v>24.76</v>
+        <v>24.8</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -529,10 +541,10 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>9.15</v>
+        <v>0.34</v>
       </c>
       <c r="D6" t="n">
-        <v>24.76</v>
+        <v>24.8</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -548,13 +560,13 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>9.140000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="D7" t="n">
         <v>24.71</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="8">
@@ -567,7 +579,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>9.140000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="D8" t="n">
         <v>24.71</v>
@@ -586,7 +598,7 @@
         <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>9.140000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="D9" t="n">
         <v>24.71</v>
@@ -605,7 +617,7 @@
         <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>9.140000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="D10" t="n">
         <v>24.71</v>
@@ -624,7 +636,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>9.140000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="D11" t="n">
         <v>24.71</v>
@@ -643,7 +655,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="D12" t="n">
         <v>20.23</v>
@@ -662,7 +674,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="D13" t="n">
         <v>20.23</v>
@@ -681,7 +693,7 @@
         <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="D14" t="n">
         <v>20.23</v>
@@ -700,7 +712,7 @@
         <v>20</v>
       </c>
       <c r="C15" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="D15" t="n">
         <v>20.23</v>
@@ -719,7 +731,7 @@
         <v>50</v>
       </c>
       <c r="C16" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="D16" t="n">
         <v>20.23</v>
@@ -738,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="D17" t="n">
         <v>27.14</v>
@@ -757,7 +769,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="D18" t="n">
         <v>27.14</v>
@@ -776,7 +788,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="D19" t="n">
         <v>27.14</v>
@@ -795,7 +807,7 @@
         <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="D20" t="n">
         <v>27.14</v>
@@ -814,7 +826,7 @@
         <v>50</v>
       </c>
       <c r="C21" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="D21" t="n">
         <v>27.14</v>

--- a/Sensitivity_Output/Sensitivity_Penalty.xlsx
+++ b/Sensitivity_Output/Sensitivity_Penalty.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,27 +429,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>penalty</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>util_std_dev</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>avg_distance_km</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>avg_travel_hours</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>overcap_weeks_total</t>
         </is>
@@ -453,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>9.15</v>
+        <v>0.4</v>
       </c>
       <c r="D2" t="n">
-        <v>24.76</v>
+        <v>1.03</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="3">
@@ -472,10 +484,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>9.15</v>
+        <v>0.35</v>
       </c>
       <c r="D3" t="n">
-        <v>24.76</v>
+        <v>1.03</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -491,10 +503,10 @@
         <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>9.15</v>
+        <v>0.35</v>
       </c>
       <c r="D4" t="n">
-        <v>24.76</v>
+        <v>1.03</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -510,10 +522,10 @@
         <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>9.15</v>
+        <v>0.35</v>
       </c>
       <c r="D5" t="n">
-        <v>24.76</v>
+        <v>1.03</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -529,10 +541,10 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>9.15</v>
+        <v>0.35</v>
       </c>
       <c r="D6" t="n">
-        <v>24.76</v>
+        <v>1.03</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -548,13 +560,13 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>9.140000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="D7" t="n">
-        <v>24.71</v>
+        <v>1.02</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="8">
@@ -567,10 +579,10 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>9.140000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="D8" t="n">
-        <v>24.71</v>
+        <v>1.02</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -586,10 +598,10 @@
         <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>9.140000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="D9" t="n">
-        <v>24.71</v>
+        <v>1.02</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -605,10 +617,10 @@
         <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>9.140000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="D10" t="n">
-        <v>24.71</v>
+        <v>1.02</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -624,10 +636,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>9.140000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="D11" t="n">
-        <v>24.71</v>
+        <v>1.02</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -643,10 +655,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="D12" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -662,10 +674,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="D13" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -681,10 +693,10 @@
         <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="D14" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -700,10 +712,10 @@
         <v>20</v>
       </c>
       <c r="C15" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="D15" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -719,10 +731,10 @@
         <v>50</v>
       </c>
       <c r="C16" t="n">
-        <v>10.95</v>
+        <v>1.61</v>
       </c>
       <c r="D16" t="n">
-        <v>20.23</v>
+        <v>0.88</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -738,10 +750,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="D17" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -757,10 +769,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="D18" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -776,10 +788,10 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="D19" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -795,10 +807,10 @@
         <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="D20" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -814,10 +826,10 @@
         <v>50</v>
       </c>
       <c r="C21" t="n">
-        <v>10.63</v>
+        <v>0.05</v>
       </c>
       <c r="D21" t="n">
-        <v>27.14</v>
+        <v>1.18</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>

--- a/Sensitivity_Output/Sensitivity_Penalty.xlsx
+++ b/Sensitivity_Output/Sensitivity_Penalty.xlsx
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="D2" t="n">
         <v>1.03</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="3">
@@ -484,13 +484,13 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.35</v>
+        <v>0.91</v>
       </c>
       <c r="D3" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -503,13 +503,13 @@
         <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>0.35</v>
+        <v>0.91</v>
       </c>
       <c r="D4" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -522,13 +522,13 @@
         <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>0.35</v>
+        <v>0.91</v>
       </c>
       <c r="D5" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -541,13 +541,13 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>0.35</v>
+        <v>0.91</v>
       </c>
       <c r="D6" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -560,13 +560,13 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0.37</v>
+        <v>2.26</v>
       </c>
       <c r="D7" t="n">
         <v>1.02</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="8">
@@ -579,13 +579,13 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0.32</v>
+        <v>1.2</v>
       </c>
       <c r="D8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -598,13 +598,13 @@
         <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>0.32</v>
+        <v>1.2</v>
       </c>
       <c r="D9" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -617,13 +617,13 @@
         <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>0.32</v>
+        <v>1.2</v>
       </c>
       <c r="D10" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -636,13 +636,13 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>0.32</v>
+        <v>1.2</v>
       </c>
       <c r="D11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -655,13 +655,13 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="D12" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -674,13 +674,13 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="D13" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -693,13 +693,13 @@
         <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="D14" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -712,13 +712,13 @@
         <v>20</v>
       </c>
       <c r="C15" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="D15" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -731,13 +731,13 @@
         <v>50</v>
       </c>
       <c r="C16" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="D16" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -750,13 +750,13 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="D17" t="n">
         <v>1.18</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -769,13 +769,13 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="D18" t="n">
         <v>1.18</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -788,13 +788,13 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="D19" t="n">
         <v>1.18</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -807,13 +807,13 @@
         <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="D20" t="n">
         <v>1.18</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -826,13 +826,13 @@
         <v>50</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="D21" t="n">
         <v>1.18</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Sensitivity_Output/Sensitivity_Penalty.xlsx
+++ b/Sensitivity_Output/Sensitivity_Penalty.xlsx
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1.8</v>
+        <v>6.2</v>
       </c>
       <c r="D2" t="n">
-        <v>1.03</v>
+        <v>0.3</v>
       </c>
       <c r="E2" t="n">
-        <v>3.18</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="3">
@@ -484,13 +484,13 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.91</v>
+        <v>6.11</v>
       </c>
       <c r="D3" t="n">
-        <v>1.05</v>
+        <v>0.3</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -503,13 +503,13 @@
         <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>0.91</v>
+        <v>6.11</v>
       </c>
       <c r="D4" t="n">
-        <v>1.05</v>
+        <v>0.3</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -522,13 +522,13 @@
         <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>0.91</v>
+        <v>6.11</v>
       </c>
       <c r="D5" t="n">
-        <v>1.05</v>
+        <v>0.3</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -541,13 +541,13 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>0.91</v>
+        <v>6.11</v>
       </c>
       <c r="D6" t="n">
-        <v>1.05</v>
+        <v>0.3</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -560,13 +560,13 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>2.26</v>
+        <v>6.19</v>
       </c>
       <c r="D7" t="n">
-        <v>1.02</v>
+        <v>0.3</v>
       </c>
       <c r="E7" t="n">
-        <v>3.18</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="8">
@@ -579,13 +579,13 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2</v>
+        <v>6.11</v>
       </c>
       <c r="D8" t="n">
-        <v>1.04</v>
+        <v>0.3</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -598,13 +598,13 @@
         <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>1.2</v>
+        <v>6.11</v>
       </c>
       <c r="D9" t="n">
-        <v>1.04</v>
+        <v>0.3</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -617,13 +617,13 @@
         <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>1.2</v>
+        <v>6.11</v>
       </c>
       <c r="D10" t="n">
-        <v>1.04</v>
+        <v>0.3</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -636,13 +636,13 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>1.2</v>
+        <v>6.11</v>
       </c>
       <c r="D11" t="n">
-        <v>1.04</v>
+        <v>0.3</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -655,13 +655,13 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="D12" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -674,13 +674,13 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="D13" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -693,13 +693,13 @@
         <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="D14" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -712,13 +712,13 @@
         <v>20</v>
       </c>
       <c r="C15" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="D15" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -731,13 +731,13 @@
         <v>50</v>
       </c>
       <c r="C16" t="n">
-        <v>5.6</v>
+        <v>9.91</v>
       </c>
       <c r="D16" t="n">
-        <v>0.89</v>
+        <v>0.26</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -750,13 +750,13 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="D17" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -769,13 +769,13 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="D18" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -788,13 +788,13 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="D19" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -807,13 +807,13 @@
         <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="D20" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -826,13 +826,13 @@
         <v>50</v>
       </c>
       <c r="C21" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
       <c r="D21" t="n">
-        <v>1.18</v>
+        <v>0.52</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Sensitivity_Output/Sensitivity_Penalty.xlsx
+++ b/Sensitivity_Output/Sensitivity_Penalty.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,27 +417,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>penalty</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>util_std_dev</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>avg_travel_hours</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>overcap_weeks_total</t>
         </is>
@@ -465,7 +453,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>6.2</v>
+        <v>6.57</v>
       </c>
       <c r="D2" t="n">
         <v>0.3</v>
@@ -484,7 +472,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>6.11</v>
+        <v>6.49</v>
       </c>
       <c r="D3" t="n">
         <v>0.3</v>
@@ -503,7 +491,7 @@
         <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>6.11</v>
+        <v>6.49</v>
       </c>
       <c r="D4" t="n">
         <v>0.3</v>
@@ -522,7 +510,7 @@
         <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>6.11</v>
+        <v>6.49</v>
       </c>
       <c r="D5" t="n">
         <v>0.3</v>
@@ -541,7 +529,7 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>6.11</v>
+        <v>6.49</v>
       </c>
       <c r="D6" t="n">
         <v>0.3</v>
@@ -560,7 +548,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>6.19</v>
+        <v>6.57</v>
       </c>
       <c r="D7" t="n">
         <v>0.3</v>
@@ -579,7 +567,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>6.11</v>
+        <v>6.49</v>
       </c>
       <c r="D8" t="n">
         <v>0.3</v>
@@ -598,7 +586,7 @@
         <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>6.11</v>
+        <v>6.49</v>
       </c>
       <c r="D9" t="n">
         <v>0.3</v>
@@ -617,7 +605,7 @@
         <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>6.11</v>
+        <v>6.49</v>
       </c>
       <c r="D10" t="n">
         <v>0.3</v>
@@ -636,7 +624,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>6.11</v>
+        <v>6.49</v>
       </c>
       <c r="D11" t="n">
         <v>0.3</v>
@@ -655,7 +643,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="D12" t="n">
         <v>0.26</v>
@@ -674,7 +662,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="D13" t="n">
         <v>0.26</v>
@@ -693,7 +681,7 @@
         <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="D14" t="n">
         <v>0.26</v>
@@ -712,7 +700,7 @@
         <v>20</v>
       </c>
       <c r="C15" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="D15" t="n">
         <v>0.26</v>
@@ -731,7 +719,7 @@
         <v>50</v>
       </c>
       <c r="C16" t="n">
-        <v>9.91</v>
+        <v>10.48</v>
       </c>
       <c r="D16" t="n">
         <v>0.26</v>

--- a/Sensitivity_Output/Sensitivity_Penalty.xlsx
+++ b/Sensitivity_Output/Sensitivity_Penalty.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,27 +429,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>penalty</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>util_std_dev</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>avg_travel_hours</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>overcap_weeks_total</t>
         </is>
